--- a/results_excel/results_Dual-head.xlsx
+++ b/results_excel/results_Dual-head.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -609,6 +609,195 @@
         <v>46.68999862670898</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UDD5Dataset</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>84.83999633789062</v>
+      </c>
+      <c r="D8" t="n">
+        <v>69.27999877929688</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80.98999786376953</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UDD5Dataset</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>84.83999633789062</v>
+      </c>
+      <c r="D9" t="n">
+        <v>69.27999877929688</v>
+      </c>
+      <c r="E9" t="n">
+        <v>80.98999786376953</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UDD5Dataset</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>84.98999786376953</v>
+      </c>
+      <c r="D10" t="n">
+        <v>69.23999786376953</v>
+      </c>
+      <c r="E10" t="n">
+        <v>80.98999786376953</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VDDDataset</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>64.62000274658203</v>
+      </c>
+      <c r="D11" t="n">
+        <v>53.81999969482422</v>
+      </c>
+      <c r="E11" t="n">
+        <v>74.19999694824219</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VDDDataset</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>65.66999816894531</v>
+      </c>
+      <c r="D12" t="n">
+        <v>54.83000183105469</v>
+      </c>
+      <c r="E12" t="n">
+        <v>74.94999694824219</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LoveDADataset</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>49.66999816894531</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35.40999984741211</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53.16999816894531</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OpenEarthMapDataset</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>41.91999816894531</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28.1299991607666</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46.68999862670898</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LoveDADataset</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>51.29000091552734</v>
+      </c>
+      <c r="D15" t="n">
+        <v>36.59000015258789</v>
+      </c>
+      <c r="E15" t="n">
+        <v>54.63000106811523</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OpenEarthMapDataset</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50.58000183105469</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31.80999946594238</v>
+      </c>
+      <c r="E16" t="n">
+        <v>51.68000030517578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
